--- a/results/Int Task Remove ACC -0.1/Rando_2_permute.xlsx
+++ b/results/Int Task Remove ACC -0.1/Rando_2_permute.xlsx
@@ -440,427 +440,427 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6507146028554935</v>
+        <v>0.6659933755349978</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6600521709444604</v>
+        <v>0.6622133163320636</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6479715919286764</v>
+        <v>0.6622133163320636</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6526800099401016</v>
+        <v>0.660447294848022</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.657970293490741</v>
+        <v>0.6594997269389885</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.657970293490741</v>
+        <v>0.6348846019363745</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.657970293490741</v>
+        <v>0.6352298794397946</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6639307071818207</v>
+        <v>0.6374306587943396</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6611570589554043</v>
+        <v>0.6435303992526444</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6885217600204638</v>
+        <v>0.6431454877822826</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6745244045543561</v>
+        <v>0.6363948262840797</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6784143689907733</v>
+        <v>0.6290610834808057</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6598017231778952</v>
+        <v>0.624984377408736</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6056685326241041</v>
+        <v>0.6360789703144019</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.598000940516467</v>
+        <v>0.6276787577012688</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.598000940516467</v>
+        <v>0.6377747205319024</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5406257887280999</v>
+        <v>0.6348449679694328</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5336577482946452</v>
+        <v>0.6359204344466345</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5350298616409823</v>
+        <v>0.6313309183360347</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5390963552798522</v>
+        <v>0.623474153061031</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5302421756956733</v>
+        <v>0.6245700444046323</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5447829784999103</v>
+        <v>0.6346954287690079</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.541969696306552</v>
+        <v>0.6318233035081653</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.545789389476428</v>
+        <v>0.6289193251818664</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5492638051428841</v>
+        <v>0.6307057715323074</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5561832149420541</v>
+        <v>0.6334589948923245</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5479415381966886</v>
+        <v>0.6393413564153776</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5476551037607529</v>
+        <v>0.5951774458899091</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5461346669798479</v>
+        <v>0.6199511067602904</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5764147745702632</v>
+        <v>0.6115124759460725</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5641768754525688</v>
+        <v>0.6100418855653092</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5470834506547385</v>
+        <v>0.6030060053970278</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5250119509783754</v>
+        <v>0.6030060053970278</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5250119509783754</v>
+        <v>0.6046837622798431</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5036387872103377</v>
+        <v>0.6023346594907303</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5035595192764539</v>
+        <v>0.6470894322227555</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5055134981620052</v>
+        <v>0.6511938577563674</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5055134981620052</v>
+        <v>0.6466415440809953</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.4714129679421996</v>
+        <v>0.6590841781690275</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.4920420830056844</v>
+        <v>0.6910432584081151</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4979640784956794</v>
+        <v>0.6919115583832649</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5066470782471768</v>
+        <v>0.7119870136754207</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5148004903913161</v>
+        <v>0.7121941801774727</v>
       </c>
     </row>
     <row r="45">
@@ -870,177 +870,177 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.496973958781647</v>
+        <v>0.7157172264782132</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5044854465532309</v>
+        <v>0.6400559835861883</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5044854465532309</v>
+        <v>0.5883548110529651</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.485031490767231</v>
+        <v>0.6039277990698905</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4847156347975531</v>
+        <v>0.5757169249682806</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4913690350271869</v>
+        <v>0.51664894080047</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.495921348702559</v>
+        <v>0.5167204278328682</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5207640650736244</v>
+        <v>0.5142524231429298</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5184047498513118</v>
+        <v>0.5128088227641945</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5176823417790156</v>
+        <v>0.51458748821315</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5161811140986531</v>
+        <v>0.5138855050072533</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5293461562589814</v>
+        <v>0.5282269222109237</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5256849989568729</v>
+        <v>0.5080060613222572</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5245993200464714</v>
+        <v>0.5075713034517537</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5418831337775255</v>
+        <v>0.5087056129964398</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5345379627751947</v>
+        <v>0.5109562387511264</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5242552583089086</v>
+        <v>0.5067312092444891</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5180480441488351</v>
+        <v>0.5112120358874629</v>
       </c>
     </row>
     <row r="63">
@@ -1050,277 +1050,277 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5253331563178245</v>
+        <v>0.5154083733198724</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5254712673191926</v>
+        <v>0.5200183142968715</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5140435545686779</v>
+        <v>0.5197024583271938</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5053785481518657</v>
+        <v>0.5066803902316617</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5041547582400963</v>
+        <v>0.5213850782734374</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5053094926511817</v>
+        <v>0.5058223026897117</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4989041086563988</v>
+        <v>0.5042826568082645</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4989041086563988</v>
+        <v>0.4996739315971224</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4969399173376479</v>
+        <v>0.5009667770095759</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.49662406136797</v>
+        <v>0.5009667770095759</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4971176623059577</v>
+        <v>0.5038172616381618</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4969795513045897</v>
+        <v>0.4988530464904</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4970486068052737</v>
+        <v>0.4973632470090944</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4996841440303222</v>
+        <v>0.5002419374055653</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4996841440303222</v>
+        <v>0.5002419374055653</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4996841440303222</v>
+        <v>0.5050181951518176</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5</v>
+        <v>0.5035794578365106</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5</v>
+        <v>0.5091153260902866</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5</v>
+        <v>0.508621725152299</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5</v>
+        <v>0.5134796823641491</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5</v>
+        <v>0.5009769894427756</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5</v>
+        <v>0.5005920779724138</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5</v>
+        <v>0.5005920779724138</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5</v>
+        <v>0.500207166502052</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4996841440303222</v>
+        <v>0.500207166502052</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4996841440303222</v>
+        <v>0.4996342976301806</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5</v>
+        <v>0.4996342976301806</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5</v>
+        <v>0.4996342976301806</v>
       </c>
     </row>
   </sheetData>
